--- a/paid-workshop-assets/phase2b/Paid_Workshop_Anonymous_Capture_Sheet_v1.2.xlsx
+++ b/paid-workshop-assets/phase2b/Paid_Workshop_Anonymous_Capture_Sheet_v1.2.xlsx
@@ -797,7 +797,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SENSITIVITY  (Poll B — runs only after the procedure, before corrected placement is finalized)</t>
+          <t>SENSITIVITY — procedure runs before corrected placement; result captured in Poll B afterward</t>
         </is>
       </c>
       <c r="B37" s="4" t="n"/>
